--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.19695497961299</v>
+        <v>5.069505184187111</v>
       </c>
       <c r="D2" t="n">
-        <v>57.47561885170814</v>
+        <v>9.339788063402573</v>
       </c>
       <c r="E2" t="n">
-        <v>16.31835893019277</v>
+        <v>2.651733326156326</v>
       </c>
       <c r="F2" t="n">
-        <v>18.37234062263873</v>
+        <v>2.985505351178793</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.82616740600475</v>
+        <v>9.559252203475772</v>
       </c>
       <c r="D3" t="n">
-        <v>13.61238202683294</v>
+        <v>2.212012079360353</v>
       </c>
       <c r="E3" t="n">
-        <v>16.31835893019277</v>
+        <v>2.651733326156326</v>
       </c>
       <c r="F3" t="n">
-        <v>18.37234062263873</v>
+        <v>2.985505351178793</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.02695120193523</v>
+        <v>11.37937957031448</v>
       </c>
       <c r="D4" t="n">
-        <v>44.25923946226118</v>
+        <v>7.192126412617442</v>
       </c>
       <c r="E4" t="n">
-        <v>16.31835893019277</v>
+        <v>2.651733326156326</v>
       </c>
       <c r="F4" t="n">
-        <v>18.37234062263873</v>
+        <v>2.985505351178793</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
